--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486709_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486709_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.0643</v>
+        <v>10.3955</v>
       </c>
       <c r="E2" t="n">
-        <v>9.4481</v>
+        <v>8.5242</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6162</v>
+        <v>1.8713</v>
       </c>
       <c r="G2" t="n">
         <v>6.9439</v>
@@ -610,13 +610,13 @@
         <v>2.3169</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1997</v>
+        <v>1.5309</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9025</v>
+        <v>0.9787</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2972</v>
+        <v>0.5522</v>
       </c>
       <c r="V2" t="n">
         <v>0.7622</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3584</v>
+        <v>5.9018</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1684</v>
+        <v>5.6373</v>
       </c>
       <c r="F3" t="n">
-        <v>0.19</v>
+        <v>0.2645</v>
       </c>
       <c r="G3" t="n">
         <v>2.326</v>
@@ -688,13 +688,13 @@
         <v>2.51</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.502</v>
+        <v>0.0413</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0004</v>
+        <v>0.4685</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5017</v>
+        <v>-0.4272</v>
       </c>
       <c r="V3" t="n">
         <v>1.9899</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6286</v>
+        <v>4.5816</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2248</v>
+        <v>4.004</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4038</v>
+        <v>0.5776</v>
       </c>
       <c r="G4" t="n">
         <v>2.1285</v>
@@ -766,13 +766,13 @@
         <v>2.51</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4012</v>
+        <v>-0.4483</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6898</v>
+        <v>0.0893</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7114</v>
+        <v>-0.5376</v>
       </c>
       <c r="V4" t="n">
         <v>0.3913</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. LOPEZ ROMERA</t>
+          <t>J. MEJIA ECHEVERRY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.364</v>
+        <v>2.3098</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8901</v>
+        <v>2.1418</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5261</v>
+        <v>0.1679</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7423</v>
+        <v>2.1722</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2963</v>
+        <v>0.8</v>
       </c>
       <c r="I5" t="n">
-        <v>2.446</v>
+        <v>1.3722</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7774</v>
+        <v>3.1114</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4345</v>
+        <v>2.4557</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3428</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.965</v>
+        <v>-0.9391</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1382</v>
+        <v>-1.6557</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1032</v>
+        <v>0.7165</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5792</v>
+        <v>0.1931</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1585</v>
+        <v>-2.1239</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5792</v>
+        <v>2.3169</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4286</v>
+        <v>-0.4895</v>
       </c>
       <c r="T5" t="n">
-        <v>1.9856</v>
+        <v>0.2548</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.7444</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2277</v>
+        <v>0.434</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2856</v>
+        <v>0.8995</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.5133</v>
+        <v>-0.4655</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0427</v>
+        <v>2.1187</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5397</v>
+        <v>0.4915</v>
       </c>
       <c r="F6" t="n">
-        <v>1.503</v>
+        <v>1.6272</v>
       </c>
       <c r="G6" t="n">
         <v>0.8843</v>
@@ -922,13 +922,13 @@
         <v>0.3862</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9653</v>
+        <v>1.0413</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.6963</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2208</v>
+        <v>0.3449</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MEJIA ECHEVERRY</t>
+          <t>A. LOPEZ ROMERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4258</v>
+        <v>1.5284</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3075</v>
+        <v>1.8559</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1183</v>
+        <v>-0.3275</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1722</v>
+        <v>2.7423</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8</v>
+        <v>0.2963</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3722</v>
+        <v>2.446</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1114</v>
+        <v>1.7774</v>
       </c>
       <c r="K7" t="n">
-        <v>2.4557</v>
+        <v>0.4345</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6556999999999999</v>
+        <v>1.3428</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9391</v>
+        <v>0.965</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.6557</v>
+        <v>-0.1382</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7165</v>
+        <v>1.1032</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1931</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1239</v>
+        <v>-1.1585</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3169</v>
+        <v>0.5792</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3735</v>
+        <v>0.593</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5795</v>
+        <v>0.9514</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.794</v>
+        <v>-0.3584</v>
       </c>
       <c r="V7" t="n">
-        <v>0.434</v>
+        <v>-1.2277</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8995</v>
+        <v>0.2856</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.4655</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0772</v>
+        <v>0.6469</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4057</v>
+        <v>0.1988</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6715</v>
+        <v>0.448</v>
       </c>
       <c r="G8" t="n">
         <v>1.2055</v>
@@ -1078,13 +1078,13 @@
         <v>0.1931</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2579</v>
+        <v>0.8275</v>
       </c>
       <c r="T8" t="n">
-        <v>0.717</v>
+        <v>0.5102</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.3174</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6138</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. DAMIAN</t>
+          <t>A. CAULIN TORNERO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7676</v>
+        <v>-1.283</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4156</v>
+        <v>-0.98</v>
       </c>
       <c r="F9" t="n">
-        <v>0.648</v>
+        <v>-0.3029</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9033</v>
+        <v>2.1089</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8136</v>
+        <v>0.3728</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0896</v>
+        <v>1.7361</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.9162</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1523</v>
+        <v>0.6489</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.0684</v>
+        <v>0.0814</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0129</v>
+        <v>1.3786</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9659</v>
+        <v>-0.2761</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9788</v>
+        <v>1.6548</v>
       </c>
       <c r="P9" t="n">
+        <v>-0.9654</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-1.9308</v>
+      </c>
+      <c r="R9" t="n">
         <v>0.9654</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-0.9654</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.9308</v>
-      </c>
       <c r="S9" t="n">
-        <v>0.9487</v>
+        <v>-0.0137</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5512</v>
+        <v>0.2205</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3975</v>
+        <v>-0.2342</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.7784</v>
+        <v>-2.4128</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.0852</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.6932</v>
+        <v>-2.4128</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. CAULIN TORNERO</t>
+          <t>D. DAMIAN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9698</v>
+        <v>-2.0958</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3937</v>
+        <v>-2.7189</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5760999999999999</v>
+        <v>0.6232</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1089</v>
+        <v>-1.9033</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3728</v>
+        <v>-0.8136</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7361</v>
+        <v>-1.0896</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7302999999999999</v>
+        <v>-1.9162</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6489</v>
+        <v>0.1523</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0814</v>
+        <v>-2.0684</v>
       </c>
       <c r="M10" t="n">
-        <v>1.3786</v>
+        <v>0.0129</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2761</v>
+        <v>-0.9659</v>
       </c>
       <c r="O10" t="n">
-        <v>1.6548</v>
+        <v>0.9788</v>
       </c>
       <c r="P10" t="n">
+        <v>0.9654</v>
+      </c>
+      <c r="Q10" t="n">
         <v>-0.9654</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-1.9308</v>
-      </c>
       <c r="R10" t="n">
-        <v>0.9654</v>
+        <v>1.9308</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7006</v>
+        <v>0.6206</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1932</v>
+        <v>0.2479</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5074</v>
+        <v>0.3727</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.4128</v>
+        <v>-1.7784</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.0852</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.4128</v>
+        <v>-1.6932</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4658</v>
+        <v>-3.7941</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4965</v>
+        <v>-0.9242</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9693</v>
+        <v>-2.87</v>
       </c>
       <c r="G11" t="n">
         <v>0.2543</v>
@@ -1312,13 +1312,13 @@
         <v>0.7723</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6508</v>
+        <v>0.0208</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3036</v>
+        <v>0.2687</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3472</v>
+        <v>-0.2479</v>
       </c>
       <c r="V11" t="n">
         <v>-3.6831</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7578</v>
+        <v>20.3098</v>
       </c>
       <c r="E12" t="n">
-        <v>17.6785</v>
+        <v>18.2304</v>
       </c>
       <c r="F12" t="n">
         <v>2.0793</v>
@@ -1357,19 +1357,19 @@
         <v>18.8626</v>
       </c>
       <c r="H12" t="n">
-        <v>7.243099999999998</v>
+        <v>7.243099999999999</v>
       </c>
       <c r="I12" t="n">
         <v>11.6196</v>
       </c>
       <c r="J12" t="n">
-        <v>19.4232</v>
+        <v>19.42319999999999</v>
       </c>
       <c r="K12" t="n">
         <v>16.2125</v>
       </c>
       <c r="L12" t="n">
-        <v>3.210700000000001</v>
+        <v>3.2107</v>
       </c>
       <c r="M12" t="n">
         <v>-0.5603000000000002</v>
@@ -1390,19 +1390,19 @@
         <v>14.4808</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1721</v>
+        <v>3.7239</v>
       </c>
       <c r="T12" t="n">
-        <v>4.1343</v>
+        <v>4.6863</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9624000000000004</v>
+        <v>-0.9624999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-6.1384</v>
       </c>
       <c r="W12" t="n">
-        <v>4.7403</v>
+        <v>4.740299999999999</v>
       </c>
       <c r="X12" t="n">
         <v>-10.8788</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.2492</v>
+        <v>2.1969</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4018</v>
+        <v>1.4711</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.7258</v>
       </c>
       <c r="G13" t="n">
         <v>2.9526</v>
@@ -1468,13 +1468,13 @@
         <v>1.5446</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5006</v>
+        <v>0.4483</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3786</v>
+        <v>0.4478</v>
       </c>
       <c r="U13" t="n">
-        <v>0.122</v>
+        <v>0.0005</v>
       </c>
       <c r="V13" t="n">
         <v>0.5337</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. JIMÉNEZ VELÁZQUEZ</t>
+          <t>J. DEL CASTILLO LEON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4261</v>
+        <v>0.314</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4483</v>
+        <v>5.1072</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8744</v>
+        <v>-4.7932</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1862</v>
+        <v>-3.175</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.462</v>
+        <v>-0.1932</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2758</v>
+        <v>-2.9818</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.6688</v>
+        <v>1.1922</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6688</v>
+        <v>3.2561</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-2.0639</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4826</v>
+        <v>-4.3672</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2068</v>
+        <v>-3.4493</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2758</v>
+        <v>-0.9179</v>
       </c>
       <c r="P14" t="n">
         <v>0.1931</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1931</v>
+        <v>-1.5446</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3862</v>
+        <v>1.7377</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4192</v>
+        <v>-0.793</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4136</v>
+        <v>0.0202</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0056</v>
+        <v>-0.8132</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>4.0889</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>5.4394</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.3505</v>
       </c>
     </row>
     <row r="15">
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1005</v>
+        <v>0.204</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>0.1034</v>
       </c>
       <c r="F15" t="n">
         <v>0.1005</v>
@@ -1624,10 +1624,10 @@
         <v>0.3862</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>0.1034</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>0.1034</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. ESTEBAN GLADER</t>
+          <t>P. JIMÉNEZ VELÁZQUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3629</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2136</v>
+        <v>-0.862</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1492</v>
+        <v>0.9378</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.0068</v>
+        <v>-0.1862</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0483</v>
+        <v>-0.462</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9585</v>
+        <v>0.2758</v>
       </c>
       <c r="J16" t="n">
         <v>-0.6688</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0207</v>
+        <v>-0.6688</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6895</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3381</v>
+        <v>0.4826</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.2068</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.269</v>
+        <v>0.2758</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.3515</v>
+        <v>0.1931</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9308</v>
+        <v>-0.1931</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5792</v>
+        <v>0.3862</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0534</v>
+        <v>0.0689</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1582</v>
+        <v>-0.0001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1048</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9421</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. DEL CASTILLO LEON</t>
+          <t>J. SECO YANES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7298</v>
+        <v>-0.1733</v>
       </c>
       <c r="E17" t="n">
-        <v>4.1764</v>
+        <v>-1.6005</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.9062</v>
+        <v>1.4272</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.175</v>
+        <v>-0.9938</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1932</v>
+        <v>0.0619</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.9818</v>
+        <v>-1.0557</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1922</v>
+        <v>-1.2762</v>
       </c>
       <c r="K17" t="n">
-        <v>3.2561</v>
+        <v>0.0621</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.0639</v>
+        <v>-1.3383</v>
       </c>
       <c r="M17" t="n">
-        <v>-4.3672</v>
+        <v>0.2824</v>
       </c>
       <c r="N17" t="n">
-        <v>-3.4493</v>
+        <v>-0.0002</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9179</v>
+        <v>0.2826</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1931</v>
+        <v>0.7723</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.5446</v>
+        <v>-0.3862</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7377</v>
+        <v>1.1585</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.8369</v>
+        <v>0.0482</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9106</v>
+        <v>0.0619</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9263</v>
+        <v>-0.0137</v>
       </c>
       <c r="V17" t="n">
-        <v>4.0889</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>5.4394</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.3505</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. SECO YANES</t>
+          <t>I. ESTEBAN GLADER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7456</v>
+        <v>-0.9337</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9107</v>
+        <v>-0.8342000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1651</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9938</v>
+        <v>-1.0068</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0619</v>
+        <v>-0.0483</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0557</v>
+        <v>-0.9585</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2762</v>
+        <v>-0.6688</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0621</v>
+        <v>0.0207</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3383</v>
+        <v>-0.6895</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2824</v>
+        <v>-0.3381</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0002</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2826</v>
+        <v>-0.269</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7723</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.3862</v>
+        <v>-1.9308</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1585</v>
+        <v>0.5792</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5241</v>
+        <v>0.4826</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2484</v>
+        <v>0.5377</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2757</v>
+        <v>-0.0551</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.9421</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.7299</v>
+        <v>-2.7699</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0039</v>
+        <v>-2.1073</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.726</v>
+        <v>-0.6626</v>
       </c>
       <c r="G19" t="n">
         <v>-2.8003</v>
@@ -1936,13 +1936,13 @@
         <v>0.7723</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0221</v>
+        <v>-0.0622</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0279</v>
+        <v>-0.1313</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0058</v>
+        <v>0.0692</v>
       </c>
       <c r="V19" t="n">
         <v>0.2856</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. EDOMWONYI IBRAHIM</t>
+          <t>M. SOSA FRANCO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7945</v>
+        <v>-2.9075</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8062</v>
+        <v>-0.0156</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.6007</v>
+        <v>-2.8919</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9735</v>
+        <v>-1.9889</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0692</v>
+        <v>-1.5661</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9043</v>
+        <v>-0.4227</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6961</v>
+        <v>0.1915</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6554</v>
+        <v>0.2276</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0407</v>
+        <v>-0.0361</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.6695</v>
+        <v>-2.1804</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7246</v>
+        <v>-1.7937</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.945</v>
+        <v>-0.3866</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -2014,28 +2014,28 @@
         <v>0.1931</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0221</v>
+        <v>-0.5102</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3032</v>
+        <v>-0.014</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3253</v>
+        <v>-0.4962</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.7989</v>
+        <v>-0.4084</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.7989</v>
+        <v>-0.4084</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. SOSA FRANCO</t>
+          <t>I. EDOMWONYI IBRAHIM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0868</v>
+        <v>-3.2827</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1913</v>
+        <v>1.3925</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.2781</v>
+        <v>-4.6752</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.9889</v>
+        <v>-0.9735</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.5661</v>
+        <v>-0.0692</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4227</v>
+        <v>-0.9043</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1915</v>
+        <v>1.6961</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2276</v>
+        <v>1.6554</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0361</v>
+        <v>0.0407</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.1804</v>
+        <v>-2.6695</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.7937</v>
+        <v>-1.7246</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3866</v>
+        <v>-0.945</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2092,22 +2092,22 @@
         <v>0.1931</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6896</v>
+        <v>-0.5103</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1928</v>
+        <v>-0.1105</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8824</v>
+        <v>-0.3998</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.4084</v>
+        <v>-1.7989</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.4084</v>
+        <v>-1.7989</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.8477</v>
+        <v>-4.2079</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7358</v>
+        <v>-1.3221</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.1119</v>
+        <v>-2.8857</v>
       </c>
       <c r="G22" t="n">
         <v>-5.2744</v>
@@ -2170,13 +2170,13 @@
         <v>1.9308</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9984</v>
+        <v>-0.3586</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3866</v>
+        <v>0.0271</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6117</v>
+        <v>-0.3856</v>
       </c>
       <c r="V22" t="n">
         <v>2.0044</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.236499999999999</v>
+        <v>-6.8946</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.3427</v>
+        <v>-3.4119</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.8938</v>
+        <v>-3.4828</v>
       </c>
       <c r="G23" t="n">
         <v>-5.4164</v>
@@ -2248,13 +2248,13 @@
         <v>1.7377</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.0521</v>
+        <v>-0.7103</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9106</v>
+        <v>0.0202</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1416</v>
+        <v>-0.7305</v>
       </c>
       <c r="V23" t="n">
         <v>0.7766999999999999</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-19.7579</v>
+        <v>-18.3789</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0793</v>
+        <v>-2.079400000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-17.6786</v>
+        <v>-16.2997</v>
       </c>
       <c r="G24" t="n">
         <v>-18.8627</v>
@@ -2302,7 +2302,7 @@
         <v>0.5604000000000002</v>
       </c>
       <c r="K24" t="n">
-        <v>8.969600000000002</v>
+        <v>8.9696</v>
       </c>
       <c r="L24" t="n">
         <v>-8.4091</v>
@@ -2326,16 +2326,16 @@
         <v>10.6194</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.172099999999999</v>
+        <v>-1.7932</v>
       </c>
       <c r="T24" t="n">
-        <v>0.9623</v>
+        <v>0.9623999999999998</v>
       </c>
       <c r="U24" t="n">
-        <v>-4.134399999999999</v>
+        <v>-2.7554</v>
       </c>
       <c r="V24" t="n">
-        <v>6.1385</v>
+        <v>6.138500000000001</v>
       </c>
       <c r="W24" t="n">
         <v>10.8788</v>
